--- a/data/satisfaction_detail/2026/9月/展览主承办.xlsx
+++ b/data/satisfaction_detail/2026/9月/展览主承办.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.26</v>
+        <v>9.4</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>9.73</v>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>9.859999999999999</v>
@@ -514,7 +514,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -553,7 +553,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
         <v>9.859999999999999</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>10</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>9.9</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>9.710000000000001</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.43</v>
+        <v>9.57</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>10</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9.15</v>
+        <v>9.42</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>9.43</v>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>9</v>
